--- a/saidas/historico_runs/historico_runs_2026_07_29.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_07_29.xlsx
@@ -4489,7 +4489,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -4498,22 +4498,22 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>0.093</v>
+        <v>0.191</v>
       </c>
       <c r="J66" t="n">
-        <v>0.653</v>
+        <v>0.664</v>
       </c>
       <c r="K66" t="n">
-        <v>0.226</v>
+        <v>0.19</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
         <v>1</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R66" t="n">
-        <v>0.327</v>
+        <v>0.314</v>
       </c>
     </row>
   </sheetData>
@@ -4549,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O485"/>
+  <dimension ref="A1:O484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33623,7 +33623,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>BBDC4</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -33637,13 +33637,13 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>0.3076</v>
+        <v>0.3362</v>
       </c>
       <c r="F482" t="n">
-        <v>1.106818</v>
+        <v>1.128108</v>
       </c>
       <c r="G482" t="n">
-        <v>1.4416</v>
+        <v>2.686</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>0.5767</v>
+        <v>0.5923</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         </is>
       </c>
       <c r="L482" t="n">
-        <v>0.5767</v>
+        <v>0.5923</v>
       </c>
       <c r="M482" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         </is>
       </c>
       <c r="O482" t="n">
-        <v>0.2444</v>
+        <v>0.1909</v>
       </c>
     </row>
     <row r="483">
@@ -33686,31 +33686,31 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>0.2293</v>
+        <v>0.1902</v>
       </c>
       <c r="F483" t="n">
-        <v>1.143976</v>
+        <v>1.17222</v>
       </c>
       <c r="G483" t="n">
-        <v>1.06</v>
+        <v>1.4256</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -33719,15 +33719,15 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>0.5599</v>
+        <v>0.5564</v>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="L483" t="n">
-        <v>0.5599</v>
+        <v>0.5564</v>
       </c>
       <c r="M483" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         </is>
       </c>
       <c r="O483" t="n">
-        <v>-0.0577</v>
+        <v>-0.1354</v>
       </c>
     </row>
     <row r="484">
@@ -33749,31 +33749,31 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>0.2226</v>
+        <v>0.1881</v>
       </c>
       <c r="F484" t="n">
-        <v>1.159549</v>
+        <v>1.181753</v>
       </c>
       <c r="G484" t="n">
-        <v>1.7351</v>
+        <v>1.9777</v>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>aprovado_executor_nivel_A</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -33782,91 +33782,28 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>0.5809</v>
+        <v>0.6371</v>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>RV_RANK</t>
         </is>
       </c>
       <c r="L484" t="n">
-        <v>0.5809</v>
+        <v>0.6371</v>
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Sem estrutura com edge positivo — não operar</t>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="O484" t="n">
-        <v>-0.1354</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>BHIA3</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E485" t="n">
-        <v>0.2112</v>
-      </c>
-      <c r="F485" t="n">
-        <v>1.154009</v>
-      </c>
-      <c r="G485" t="n">
-        <v>1.9402</v>
-      </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="I485" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J485" t="n">
-        <v>0.6287</v>
-      </c>
-      <c r="K485" t="inlineStr">
-        <is>
-          <t>RV_RANK</t>
-        </is>
-      </c>
-      <c r="L485" t="n">
-        <v>0.6287</v>
-      </c>
-      <c r="M485" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="N485" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="O485" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6643</v>
       </c>
     </row>
   </sheetData>
@@ -33880,7 +33817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34089,13 +34026,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -34103,7 +34040,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="G8" t="n">
         <v>0.392</v>
@@ -34293,52 +34230,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46174</v>
+        <v>46156</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46227</v>
+        <v>46180</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46180</v>
+        <v>46227</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34443,52 +34380,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46180</v>
+        <v>46228</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>Alerta CALL, Compra PUT, Monitorar CALL, Monitorar PUT</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.444</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46183</v>
+        <v>46164</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46228</v>
+        <v>46180</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alerta CALL, Compra PUT, Monitorar CALL, Monitorar PUT</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.444</v>
-      </c>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -34539,121 +34476,121 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46200</v>
+        <v>46224</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46205</v>
+        <v>46228</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Compra PUT, Monitorar PUT</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.515</v>
+        <v>-0.01</v>
       </c>
       <c r="G26" t="n">
-        <v>0.515</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46170</v>
+        <v>46205</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46183</v>
+        <v>46209</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Monitorar CALL, Monitorar PUT</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Alerta CALL</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>46205</v>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>46209</v>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Alerta CALL</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.06</v>
+        <v>0.515</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>AXIA3</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46224</v>
+        <v>46170</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46228</v>
+        <v>46183</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Compra PUT, Monitorar PUT</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.011</v>
-      </c>
+          <t>Monitorar CALL, Monitorar PUT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -34666,17 +34603,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AURE3</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46182</v>
+        <v>46168</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -34730,137 +34667,137 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.644</v>
+        <v>0.647</v>
       </c>
       <c r="G33" t="n">
-        <v>0.653</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46160</v>
+        <v>46173</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46174</v>
+        <v>46212</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+          <t>Alerta CALL, Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.648</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46173</v>
+        <v>46160</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46212</v>
+        <v>46174</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.648</v>
-      </c>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46227</v>
+        <v>46170</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alerta PUT, Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.164</v>
-      </c>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46167</v>
+        <v>46200</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46170</v>
+        <v>46202</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>Alerta CALL</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.054</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46230</v>
+        <v>46163</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46232</v>
+        <v>46227</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Alerta PUT, Monitorar CALL</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-0.058</v>
+        <v>0.164</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.058</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="39">
@@ -34916,44 +34853,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46200</v>
+        <v>46153</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46202</v>
+        <v>46154</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.054</v>
-      </c>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46210</v>
+        <v>46185</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46211</v>
+        <v>46186</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -34961,34 +34894,38 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.385</v>
+        <v>0.644</v>
       </c>
       <c r="G42" t="n">
-        <v>0.385</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46154</v>
+        <v>46228</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+          <t>Alerta CALL, Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -35020,17 +34957,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46185</v>
+        <v>46210</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46186</v>
+        <v>46211</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -35038,87 +34975,114 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.644</v>
+        <v>0.385</v>
       </c>
       <c r="G45" t="n">
-        <v>0.644</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46154</v>
+        <v>46230</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.065</v>
+        <v>-0.058</v>
       </c>
       <c r="G46" t="n">
-        <v>0.065</v>
+        <v>-0.058</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ECOR3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46180</v>
+        <v>46202</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46180</v>
+        <v>46202</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Alerta CALL</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>-0.162</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.162</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>ECOR3</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46202</v>
+        <v>46180</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46202</v>
+        <v>46180</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Alerta CALL</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>-0.162</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-0.162</v>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GOAU4</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Alerta CALL</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.191</v>
       </c>
     </row>
   </sheetData>

--- a/saidas/historico_runs/historico_runs_2026_07_29.xlsx
+++ b/saidas/historico_runs/historico_runs_2026_07_29.xlsx
@@ -4489,7 +4489,7 @@
         <v>49</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -4498,22 +4498,22 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>0.191</v>
+        <v>0.265</v>
       </c>
       <c r="J66" t="n">
-        <v>0.664</v>
+        <v>0.665</v>
       </c>
       <c r="K66" t="n">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>1</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R66" t="n">
-        <v>0.314</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -4549,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O484"/>
+  <dimension ref="A1:O483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33623,31 +33623,31 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
+          <t>Compra CALL</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>0.3362</v>
+        <v>0.1926</v>
       </c>
       <c r="F482" t="n">
-        <v>1.128108</v>
+        <v>1.172216</v>
       </c>
       <c r="G482" t="n">
-        <v>2.686</v>
+        <v>1.3885</v>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>alerta_executor_nivel_B</t>
+          <t>aprovado_executor_nivel_A</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -33656,28 +33656,28 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>0.5923</v>
+        <v>0.5522</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HAR</t>
         </is>
       </c>
       <c r="L482" t="n">
-        <v>0.5923</v>
+        <v>0.5522</v>
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Call delta~45 naked (quase ATM, ~0.9σ, 20d)</t>
+          <t>Sem estrutura com edge positivo — não operar</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>baixa</t>
         </is>
       </c>
       <c r="O482" t="n">
-        <v>0.1909</v>
+        <v>-0.1354</v>
       </c>
     </row>
     <row r="483">
@@ -33686,31 +33686,31 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Compra CALL</t>
+          <t>Alerta PUT</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>0.1902</v>
+        <v>0.1929</v>
       </c>
       <c r="F483" t="n">
-        <v>1.17222</v>
+        <v>1.201075</v>
       </c>
       <c r="G483" t="n">
-        <v>1.4256</v>
+        <v>2.0233</v>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>aprovado_executor_nivel_A</t>
+          <t>alerta_executor_nivel_B</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -33719,91 +33719,28 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>0.5564</v>
+        <v>0.6384</v>
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>HAR</t>
+          <t>RV_RANK</t>
         </is>
       </c>
       <c r="L483" t="n">
-        <v>0.5564</v>
+        <v>0.6384</v>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Sem estrutura com edge positivo — não operar</t>
+          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>baixa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="O483" t="n">
-        <v>-0.1354</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>BHIA3</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Alerta PUT</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E484" t="n">
-        <v>0.1881</v>
-      </c>
-      <c r="F484" t="n">
-        <v>1.181753</v>
-      </c>
-      <c r="G484" t="n">
-        <v>1.9777</v>
-      </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>alerta_executor_nivel_B</t>
-        </is>
-      </c>
-      <c r="I484" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
-      </c>
-      <c r="J484" t="n">
-        <v>0.6371</v>
-      </c>
-      <c r="K484" t="inlineStr">
-        <is>
-          <t>RV_RANK</t>
-        </is>
-      </c>
-      <c r="L484" t="n">
-        <v>0.6371</v>
-      </c>
-      <c r="M484" t="inlineStr">
-        <is>
-          <t>Put delta~-45 naked (quase ATM, ~0.9σ, 20d)</t>
-        </is>
-      </c>
-      <c r="N484" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="O484" t="n">
-        <v>0.6643</v>
+        <v>0.6655</v>
       </c>
     </row>
   </sheetData>
@@ -33817,7 +33754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34230,52 +34167,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46180</v>
+        <v>46227</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46174</v>
+        <v>46156</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46227</v>
+        <v>46180</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.08</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -34380,52 +34317,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46183</v>
+        <v>46164</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46228</v>
+        <v>46180</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Alerta CALL, Compra PUT, Monitorar CALL, Monitorar PUT</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.444</v>
-      </c>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46180</v>
+        <v>46228</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>Alerta CALL, Compra PUT, Monitorar CALL, Monitorar PUT</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.444</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -34476,71 +34413,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46224</v>
+        <v>46200</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46228</v>
+        <v>46205</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Compra PUT, Monitorar PUT</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-0.01</v>
+        <v>0.515</v>
       </c>
       <c r="G26" t="n">
-        <v>0.011</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>AXIA3</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46205</v>
+        <v>46170</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46209</v>
+        <v>46183</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.06</v>
-      </c>
+          <t>Monitorar CALL, Monitorar PUT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46200</v>
+        <v>46205</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -34548,49 +34481,53 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.515</v>
+        <v>0.06</v>
       </c>
       <c r="G28" t="n">
-        <v>0.515</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46170</v>
+        <v>46224</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46183</v>
+        <v>46228</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Monitorar CALL, Monitorar PUT</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+          <t>Compra PUT, Monitorar PUT</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.011</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AURE3</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46182</v>
+        <v>46168</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -34603,17 +34540,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -34670,134 +34607,134 @@
         <v>0.647</v>
       </c>
       <c r="G33" t="n">
-        <v>0.664</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46173</v>
+        <v>46160</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46212</v>
+        <v>46174</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.648</v>
-      </c>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46160</v>
+        <v>46173</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46174</v>
+        <v>46212</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+          <t>Alerta CALL, Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.648</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46170</v>
+        <v>46227</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Monitorar CALL</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>Alerta PUT, Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.164</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46200</v>
+        <v>46167</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46202</v>
+        <v>46170</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alerta CALL</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.054</v>
-      </c>
+          <t>Monitorar CALL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46163</v>
+        <v>46200</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46227</v>
+        <v>46202</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alerta PUT, Monitorar CALL</t>
+          <t>Alerta CALL</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.164</v>
+        <v>0.054</v>
       </c>
       <c r="G38" t="n">
-        <v>0.164</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="39">
@@ -34853,79 +34790,79 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BOVA11</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46153</v>
+        <v>46210</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46154</v>
+        <v>46211</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Alerta PUT</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.385</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46185</v>
+        <v>46154</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46186</v>
+        <v>46228</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alerta PUT</t>
+          <t>Alerta CALL, Alerta PUT</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.644</v>
+        <v>0.065</v>
       </c>
       <c r="G42" t="n">
-        <v>0.644</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>BOVA11</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D43" s="1" t="n">
         <v>46154</v>
       </c>
-      <c r="D43" s="1" t="n">
-        <v>46228</v>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alerta CALL, Alerta PUT</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.065</v>
-      </c>
+          <t>Alerta PUT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -34957,17 +34894,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46210</v>
+        <v>46185</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46211</v>
+        <v>46186</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -34975,10 +34912,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.385</v>
+        <v>0.644</v>
       </c>
       <c r="G45" t="n">
-        <v>0.385</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="46">
@@ -35011,78 +34948,51 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>ECOR3</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46202</v>
+        <v>46180</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46202</v>
+        <v>46180</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Alerta CALL</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>-0.162</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.162</v>
-      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ECOR3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46180</v>
+        <v>46202</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46180</v>
+        <v>46202</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Alerta CALL</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>GOAU4</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>46232</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Alerta CALL</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.191</v>
+      <c r="F48" t="n">
+        <v>-0.162</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.162</v>
       </c>
     </row>
   </sheetData>
